--- a/content/post/drafts/weekly-recap/2025Ruka/ladies_race1.xlsx
+++ b/content/post/drafts/weekly-recap/2025Ruka/ladies_race1.xlsx
@@ -662,13 +662,13 @@
         <v>69.8879824110691</v>
       </c>
       <c r="F2" t="n">
-        <v>68.2027155548745</v>
+        <v>82.8116550433661</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>31.7972844451255</v>
+        <v>17.1883449566339</v>
       </c>
     </row>
     <row r="3">
@@ -688,13 +688,13 @@
         <v>48.3523878188466</v>
       </c>
       <c r="F3" t="n">
-        <v>85.3021440711385</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
         <v>95</v>
       </c>
       <c r="H3" t="n">
-        <v>9.6978559288615</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="4">
@@ -714,13 +714,13 @@
         <v>107.764245226608</v>
       </c>
       <c r="F4" t="n">
-        <v>53.9008029718327</v>
+        <v>65.4462900186506</v>
       </c>
       <c r="G4" t="n">
         <v>90</v>
       </c>
       <c r="H4" t="n">
-        <v>36.0991970281673</v>
+        <v>24.5537099813494</v>
       </c>
     </row>
     <row r="5">
@@ -740,13 +740,13 @@
         <v>57.5301617524124</v>
       </c>
       <c r="F5" t="n">
-        <v>61.7069756049925</v>
+        <v>74.9245354234993</v>
       </c>
       <c r="G5" t="n">
         <v>85</v>
       </c>
       <c r="H5" t="n">
-        <v>23.2930243950075</v>
+        <v>10.0754645765007</v>
       </c>
     </row>
     <row r="6">
@@ -766,13 +766,13 @@
         <v>60.4676363092101</v>
       </c>
       <c r="F6" t="n">
-        <v>61.1662328944813</v>
+        <v>74.2679662759845</v>
       </c>
       <c r="G6" t="n">
         <v>80</v>
       </c>
       <c r="H6" t="n">
-        <v>18.8337671055187</v>
+        <v>5.73203372401549</v>
       </c>
     </row>
     <row r="7">
@@ -792,13 +792,13 @@
         <v>45.0381819460524</v>
       </c>
       <c r="F7" t="n">
-        <v>67.7726259215564</v>
+        <v>82.2894407288435</v>
       </c>
       <c r="G7" t="n">
         <v>75</v>
       </c>
       <c r="H7" t="n">
-        <v>7.2273740784436</v>
+        <v>-7.2894407288435</v>
       </c>
     </row>
     <row r="8">
@@ -818,13 +818,13 @@
         <v>63.5596775852473</v>
       </c>
       <c r="F8" t="n">
-        <v>57.1866657053301</v>
+        <v>69.4359805902425</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>14.8133342946699</v>
+        <v>2.56401940975751</v>
       </c>
     </row>
     <row r="9">
@@ -844,13 +844,13 @@
         <v>48.6373246839505</v>
       </c>
       <c r="F9" t="n">
-        <v>60.4409439815829</v>
+        <v>73.3873213519067</v>
       </c>
       <c r="G9" t="n">
         <v>69</v>
       </c>
       <c r="H9" t="n">
-        <v>8.5590560184171</v>
+        <v>-4.38732135190671</v>
       </c>
     </row>
     <row r="10">
@@ -870,13 +870,13 @@
         <v>46.0932452319194</v>
       </c>
       <c r="F10" t="n">
-        <v>52.6982578381954</v>
+        <v>63.986161166439</v>
       </c>
       <c r="G10" t="n">
         <v>66</v>
       </c>
       <c r="H10" t="n">
-        <v>13.3017421618046</v>
+        <v>2.013838833561</v>
       </c>
     </row>
     <row r="11">
@@ -896,13 +896,13 @@
         <v>63.5396758665113</v>
       </c>
       <c r="F11" t="n">
-        <v>51.5641268148047</v>
+        <v>62.6091006444508</v>
       </c>
       <c r="G11" t="n">
         <v>63</v>
       </c>
       <c r="H11" t="n">
-        <v>11.4358731851953</v>
+        <v>0.390899355549202</v>
       </c>
     </row>
     <row r="12">
@@ -922,13 +922,13 @@
         <v>50.7623972512697</v>
       </c>
       <c r="F12" t="n">
-        <v>57.0037288919872</v>
+        <v>69.2138589319179</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9962711080128</v>
+        <v>-9.2138589319179</v>
       </c>
     </row>
     <row r="13">
@@ -948,13 +948,13 @@
         <v>26.8234895160208</v>
       </c>
       <c r="F13" t="n">
-        <v>59.6552296787326</v>
+        <v>72.4333079921611</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6552296787326</v>
+        <v>-14.4333079921611</v>
       </c>
     </row>
     <row r="14">
@@ -974,13 +974,13 @@
         <v>69.3120515467306</v>
       </c>
       <c r="F14" t="n">
-        <v>40.1811441371637</v>
+        <v>48.7878967936015</v>
       </c>
       <c r="G14" t="n">
         <v>56</v>
       </c>
       <c r="H14" t="n">
-        <v>15.8188558628363</v>
+        <v>7.2121032063985</v>
       </c>
     </row>
     <row r="15">
@@ -1000,13 +1000,13 @@
         <v>28.4283138570215</v>
       </c>
       <c r="F15" t="n">
-        <v>64.4081168215604</v>
+        <v>78.2042578338169</v>
       </c>
       <c r="G15" t="n">
         <v>54</v>
       </c>
       <c r="H15" t="n">
-        <v>-10.4081168215604</v>
+        <v>-24.2042578338169</v>
       </c>
     </row>
     <row r="16">
@@ -1026,13 +1026,13 @@
         <v>78.6012958972219</v>
       </c>
       <c r="F16" t="n">
-        <v>25.8206437501528</v>
+        <v>31.3513945279042</v>
       </c>
       <c r="G16" t="n">
         <v>52</v>
       </c>
       <c r="H16" t="n">
-        <v>26.1793562498472</v>
+        <v>20.6486054720958</v>
       </c>
     </row>
     <row r="17">
@@ -1052,13 +1052,13 @@
         <v>86.9155170067809</v>
       </c>
       <c r="F17" t="n">
-        <v>26.3853425650831</v>
+        <v>32.0370511485381</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
       </c>
       <c r="H17" t="n">
-        <v>23.6146574349169</v>
+        <v>17.9629488514619</v>
       </c>
     </row>
     <row r="18">
@@ -1078,13 +1078,13 @@
         <v>50.572568008105</v>
       </c>
       <c r="F18" t="n">
-        <v>34.2566034162102</v>
+        <v>41.5943265892122</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
       </c>
       <c r="H18" t="n">
-        <v>13.7433965837898</v>
+        <v>6.4056734107878</v>
       </c>
     </row>
     <row r="19">
@@ -1104,13 +1104,13 @@
         <v>-23.4303803952962</v>
       </c>
       <c r="F19" t="n">
-        <v>72.0077605196961</v>
+        <v>87.4317360546241</v>
       </c>
       <c r="G19" t="n">
         <v>46</v>
       </c>
       <c r="H19" t="n">
-        <v>-26.0077605196961</v>
+        <v>-41.4317360546241</v>
       </c>
     </row>
     <row r="20">
@@ -1130,13 +1130,13 @@
         <v>55.7019593760128</v>
       </c>
       <c r="F20" t="n">
-        <v>29.1602676582945</v>
+        <v>35.4063618529676</v>
       </c>
       <c r="G20" t="n">
         <v>44</v>
       </c>
       <c r="H20" t="n">
-        <v>14.8397323417055</v>
+        <v>8.5936381470324</v>
       </c>
     </row>
     <row r="21">
@@ -1156,13 +1156,13 @@
         <v>56.7001757843379</v>
       </c>
       <c r="F21" t="n">
-        <v>25.8007441013787</v>
+        <v>31.3272323983415</v>
       </c>
       <c r="G21" t="n">
         <v>42</v>
       </c>
       <c r="H21" t="n">
-        <v>16.1992558986213</v>
+        <v>10.6727676016585</v>
       </c>
     </row>
     <row r="22">
@@ -1182,13 +1182,13 @@
         <v>48.6462265727466</v>
       </c>
       <c r="F22" t="n">
-        <v>31.8479202308955</v>
+        <v>38.6697063680342</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
       </c>
       <c r="H22" t="n">
-        <v>8.1520797691045</v>
+        <v>1.3302936319658</v>
       </c>
     </row>
     <row r="23">
@@ -1208,13 +1208,13 @@
         <v>-0.905233355665359</v>
       </c>
       <c r="F23" t="n">
-        <v>54.1543031025553</v>
+        <v>65.7540895719097</v>
       </c>
       <c r="G23" t="n">
         <v>38</v>
       </c>
       <c r="H23" t="n">
-        <v>-16.1543031025553</v>
+        <v>-27.7540895719097</v>
       </c>
     </row>
     <row r="24">
@@ -1234,13 +1234,13 @@
         <v>94.7236051532379</v>
       </c>
       <c r="F24" t="n">
-        <v>2.75113677615925</v>
+        <v>3.34042695852944</v>
       </c>
       <c r="G24" t="n">
         <v>36</v>
       </c>
       <c r="H24" t="n">
-        <v>33.2488632238408</v>
+        <v>32.6595730414706</v>
       </c>
     </row>
     <row r="25">
@@ -1260,13 +1260,13 @@
         <v>72.4112056297829</v>
       </c>
       <c r="F25" t="n">
-        <v>7.06716199869954</v>
+        <v>8.58093958298503</v>
       </c>
       <c r="G25" t="n">
         <v>34</v>
       </c>
       <c r="H25" t="n">
-        <v>26.9328380013005</v>
+        <v>25.419060417015</v>
       </c>
     </row>
     <row r="26">
@@ -1286,13 +1286,13 @@
         <v>42.2124293893914</v>
       </c>
       <c r="F26" t="n">
-        <v>27.8036942690328</v>
+        <v>33.7592120783789</v>
       </c>
       <c r="G26" t="n">
         <v>32</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1963057309672</v>
+        <v>-1.7592120783789</v>
       </c>
     </row>
     <row r="27">
@@ -1312,13 +1312,13 @@
         <v>79.8934809011519</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.233748889400793</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>30</v>
       </c>
       <c r="H27" t="n">
-        <v>30.2337488894008</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
@@ -1338,13 +1338,13 @@
         <v>15.3384815099532</v>
       </c>
       <c r="F28" t="n">
-        <v>21.069858738753</v>
+        <v>25.5829970916951</v>
       </c>
       <c r="G28" t="n">
         <v>28</v>
       </c>
       <c r="H28" t="n">
-        <v>6.930141261247</v>
+        <v>2.4170029083049</v>
       </c>
     </row>
     <row r="29">
@@ -1364,13 +1364,13 @@
         <v>44.4489203748633</v>
       </c>
       <c r="F29" t="n">
-        <v>14.319071184153</v>
+        <v>17.3861989775088</v>
       </c>
       <c r="G29" t="n">
         <v>26</v>
       </c>
       <c r="H29" t="n">
-        <v>11.680928815847</v>
+        <v>8.6138010224912</v>
       </c>
     </row>
     <row r="30">
@@ -1390,13 +1390,13 @@
         <v>51.5546562517588</v>
       </c>
       <c r="F30" t="n">
-        <v>4.06941377127184</v>
+        <v>4.94107729748895</v>
       </c>
       <c r="G30" t="n">
         <v>24</v>
       </c>
       <c r="H30" t="n">
-        <v>19.9305862287282</v>
+        <v>19.0589227025111</v>
       </c>
     </row>
     <row r="31">
@@ -1416,13 +1416,13 @@
         <v>9.63384690997464</v>
       </c>
       <c r="F31" t="n">
-        <v>24.0626997729214</v>
+        <v>29.2169010690489</v>
       </c>
       <c r="G31" t="n">
         <v>22</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.0626997729214</v>
+        <v>-7.2169010690489</v>
       </c>
     </row>
     <row r="32">
@@ -1442,13 +1442,13 @@
         <v>36.7674248071971</v>
       </c>
       <c r="F32" t="n">
-        <v>27.1858808890776</v>
+        <v>33.0090638168941</v>
       </c>
       <c r="G32" t="n">
         <v>20</v>
       </c>
       <c r="H32" t="n">
-        <v>-7.1858808890776</v>
+        <v>-13.0090638168941</v>
       </c>
     </row>
     <row r="33">
@@ -1468,13 +1468,13 @@
         <v>-5.4014468883297</v>
       </c>
       <c r="F33" t="n">
-        <v>30.3213483492007</v>
+        <v>36.8161446287792</v>
       </c>
       <c r="G33" t="n">
         <v>19</v>
       </c>
       <c r="H33" t="n">
-        <v>-11.3213483492007</v>
+        <v>-17.8161446287792</v>
       </c>
     </row>
     <row r="34">
@@ -1494,13 +1494,13 @@
         <v>32.1080281863556</v>
       </c>
       <c r="F34" t="n">
-        <v>4.39481789560249</v>
+        <v>5.3361825931436</v>
       </c>
       <c r="G34" t="n">
         <v>18</v>
       </c>
       <c r="H34" t="n">
-        <v>13.6051821043975</v>
+        <v>12.6638174068564</v>
       </c>
     </row>
     <row r="35">
@@ -1520,13 +1520,13 @@
         <v>12.6614392427318</v>
       </c>
       <c r="F35" t="n">
-        <v>15.0600434905039</v>
+        <v>18.2858866590183</v>
       </c>
       <c r="G35" t="n">
         <v>17</v>
       </c>
       <c r="H35" t="n">
-        <v>1.9399565094961</v>
+        <v>-1.2858866590183</v>
       </c>
     </row>
     <row r="36">
@@ -1546,13 +1546,13 @@
         <v>-60.2623427534882</v>
       </c>
       <c r="F36" t="n">
-        <v>43.822198906034</v>
+        <v>53.2088611065413</v>
       </c>
       <c r="G36" t="n">
         <v>16</v>
       </c>
       <c r="H36" t="n">
-        <v>-27.822198906034</v>
+        <v>-37.2088611065413</v>
       </c>
     </row>
     <row r="37">
@@ -1572,13 +1572,13 @@
         <v>7.49501728093674</v>
       </c>
       <c r="F37" t="n">
-        <v>14.5153474995435</v>
+        <v>17.6245174431456</v>
       </c>
       <c r="G37" t="n">
         <v>15</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4846525004565</v>
+        <v>-2.6245174431456</v>
       </c>
     </row>
     <row r="38">
@@ -1598,13 +1598,13 @@
         <v>33.9070505895018</v>
       </c>
       <c r="F38" t="n">
-        <v>10.5028365276629</v>
+        <v>12.7525314561104</v>
       </c>
       <c r="G38" t="n">
         <v>14</v>
       </c>
       <c r="H38" t="n">
-        <v>3.4971634723371</v>
+        <v>1.2474685438896</v>
       </c>
     </row>
     <row r="39">
@@ -1624,13 +1624,13 @@
         <v>-2.4709146143573</v>
       </c>
       <c r="F39" t="n">
-        <v>6.10642294338102</v>
+        <v>7.41441137969503</v>
       </c>
       <c r="G39" t="n">
         <v>13</v>
       </c>
       <c r="H39" t="n">
-        <v>6.89357705661898</v>
+        <v>5.58558862030497</v>
       </c>
     </row>
     <row r="40">
@@ -1650,13 +1650,13 @@
         <v>-37.2361880955825</v>
       </c>
       <c r="F40" t="n">
-        <v>31.3878293340857</v>
+        <v>38.1110645555312</v>
       </c>
       <c r="G40" t="n">
         <v>12</v>
       </c>
       <c r="H40" t="n">
-        <v>-19.3878293340857</v>
+        <v>-26.1110645555312</v>
       </c>
     </row>
     <row r="41">
@@ -1676,13 +1676,13 @@
         <v>5.66742149514039</v>
       </c>
       <c r="F41" t="n">
-        <v>1.71037256252751</v>
+        <v>2.07673230444478</v>
       </c>
       <c r="G41" t="n">
         <v>12</v>
       </c>
       <c r="H41" t="n">
-        <v>10.2896274374725</v>
+        <v>9.92326769555522</v>
       </c>
     </row>
     <row r="42">
@@ -1702,13 +1702,13 @@
         <v>3.31166818004226</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.80981013926786</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>10</v>
       </c>
       <c r="H42" t="n">
-        <v>12.8098101392679</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -1728,13 +1728,13 @@
         <v>-40.8589077384181</v>
       </c>
       <c r="F43" t="n">
-        <v>14.5436016806224</v>
+        <v>17.6588236357656</v>
       </c>
       <c r="G43" t="n">
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>-5.5436016806224</v>
+        <v>-8.6588236357656</v>
       </c>
     </row>
     <row r="44">
@@ -1754,13 +1754,13 @@
         <v>3.59484181885705</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.72963767364509</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>8</v>
       </c>
       <c r="H44" t="n">
-        <v>10.7296376736451</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -1780,13 +1780,13 @@
         <v>-22.4131213113469</v>
       </c>
       <c r="F45" t="n">
-        <v>1.31291417671395</v>
+        <v>1.59413881132201</v>
       </c>
       <c r="G45" t="n">
         <v>7</v>
       </c>
       <c r="H45" t="n">
-        <v>5.68708582328605</v>
+        <v>5.40586118867799</v>
       </c>
     </row>
     <row r="46">
@@ -1806,13 +1806,13 @@
         <v>-18.9582942435582</v>
       </c>
       <c r="F46" t="n">
-        <v>9.71590933007489</v>
+        <v>11.7970454010358</v>
       </c>
       <c r="G46" t="n">
         <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>-3.71590933007489</v>
+        <v>-5.7970454010358</v>
       </c>
     </row>
     <row r="47">
@@ -1832,13 +1832,13 @@
         <v>-16.2756845190052</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.89306493940642</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>5</v>
       </c>
       <c r="H47" t="n">
-        <v>6.89306493940642</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -1858,13 +1858,13 @@
         <v>-28.8329347192021</v>
       </c>
       <c r="F48" t="n">
-        <v>0.344344753337726</v>
+        <v>0.418102984571832</v>
       </c>
       <c r="G48" t="n">
         <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>3.65565524666227</v>
+        <v>3.58189701542817</v>
       </c>
     </row>
     <row r="49">
@@ -1884,13 +1884,13 @@
         <v>-2.42983053991838</v>
       </c>
       <c r="F49" t="n">
-        <v>-10.7356841725455</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>13.7356841725455</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -1910,13 +1910,13 @@
         <v>-30.9262553881761</v>
       </c>
       <c r="F50" t="n">
-        <v>9.88202153339065</v>
+        <v>11.9987386381388</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>-7.88202153339065</v>
+        <v>-9.9987386381388</v>
       </c>
     </row>
     <row r="51">
@@ -1936,13 +1936,13 @@
         <v>-44.9156879104457</v>
       </c>
       <c r="F51" t="n">
-        <v>9.08884493506456</v>
+        <v>11.0356645682185</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>-8.08884493506456</v>
+        <v>-10.0356645682185</v>
       </c>
     </row>
     <row r="52">
@@ -1962,13 +1962,13 @@
         <v>-57.299012640646</v>
       </c>
       <c r="F52" t="n">
-        <v>5.43582524785748</v>
+        <v>6.60017246585164</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-5.43582524785748</v>
+        <v>-6.60017246585164</v>
       </c>
     </row>
     <row r="53">
@@ -1988,13 +1988,13 @@
         <v>-53.9287852259931</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.3191225889495</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.3191225889495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2014,13 +2014,13 @@
         <v>-62.5023971429728</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.175962770175843</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.175962770175843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2040,13 +2040,13 @@
         <v>-82.7202829538958</v>
       </c>
       <c r="F55" t="n">
-        <v>13.6683053994398</v>
+        <v>16.5960399458741</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-13.6683053994398</v>
+        <v>-16.5960399458741</v>
       </c>
     </row>
     <row r="56">
@@ -2066,13 +2066,13 @@
         <v>-81.7221504495101</v>
       </c>
       <c r="F56" t="n">
-        <v>2.06794542701618</v>
+        <v>2.51089684563639</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-2.06794542701618</v>
+        <v>-2.51089684563639</v>
       </c>
     </row>
     <row r="57">
@@ -2092,13 +2092,13 @@
         <v>-84.6667711441585</v>
       </c>
       <c r="F57" t="n">
-        <v>2.30471514501506</v>
+        <v>2.79838235192628</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-2.30471514501506</v>
+        <v>-2.79838235192628</v>
       </c>
     </row>
     <row r="58">
@@ -2118,13 +2118,13 @@
         <v>-85.0811780397626</v>
       </c>
       <c r="F58" t="n">
-        <v>3.77501594518944</v>
+        <v>4.58361981180516</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-3.77501594518944</v>
+        <v>-4.58361981180516</v>
       </c>
     </row>
     <row r="59">
@@ -2144,13 +2144,13 @@
         <v>-86.6082983374781</v>
       </c>
       <c r="F59" t="n">
-        <v>-4.07566363866445</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>4.07566363866445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2170,13 +2170,13 @@
         <v>-58.3741165863523</v>
       </c>
       <c r="F60" t="n">
-        <v>-14.836643303959</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>14.836643303959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2218,13 +2218,13 @@
         <v>-59.4025236966907</v>
       </c>
       <c r="F62" t="n">
-        <v>-21.4599065053224</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>21.4599065053224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2244,13 +2244,13 @@
         <v>-68.8011262981138</v>
       </c>
       <c r="F63" t="n">
-        <v>-14.6821365329454</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>14.6821365329454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2270,13 +2270,13 @@
         <v>-90.88707622013</v>
       </c>
       <c r="F64" t="n">
-        <v>-14.8844441835301</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>14.8844441835301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2296,13 +2296,13 @@
         <v>-97.3219799962969</v>
       </c>
       <c r="F65" t="n">
-        <v>-10.7879541015177</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>10.7879541015177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2322,13 +2322,13 @@
         <v>-78.9482682296075</v>
       </c>
       <c r="F66" t="n">
-        <v>-23.4238336897355</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>23.4238336897355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2348,13 +2348,13 @@
         <v>-136.72215044951</v>
       </c>
       <c r="F67" t="n">
-        <v>2.06794542701618</v>
+        <v>2.51089684563639</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-2.06794542701618</v>
+        <v>-2.51089684563639</v>
       </c>
     </row>
     <row r="68">
@@ -2374,13 +2374,13 @@
         <v>-101.603443082736</v>
       </c>
       <c r="F68" t="n">
-        <v>-17.1278513639015</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>17.1278513639015</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
